--- a/docs/UI introduction.xlsx
+++ b/docs/UI introduction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="19160"/>
+    <workbookView windowWidth="20900" windowHeight="19660"/>
   </bookViews>
   <sheets>
     <sheet name="UI introduction" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>Clean up transcripts(是否维持上次选项)</t>
   </si>
   <si>
-    <t>Tasks information展示内容</t>
+    <t>Task information展示内容</t>
   </si>
   <si>
     <t>transcribe文本是否展示</t>
@@ -188,7 +188,7 @@
     <t>N/N chunks 或 0/N chunks</t>
   </si>
   <si>
-    <t>有chunk进度时为当前文件名，否则 Transcribing…</t>
+    <t>当前文件名</t>
   </si>
   <si>
     <t>有转写结果无失败</t>
@@ -2056,7 +2056,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>16</v>
